--- a/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T18:12:06+00:00</t>
+    <t>2026-07-09T18:19:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T18:19:16+00:00</t>
+    <t>2026-07-15T06:27:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T06:27:44+00:00</t>
+    <t>2026-07-15T13:41:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T13:41:49+00:00</t>
+    <t>2026-07-15T16:11:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T16:11:54+00:00</t>
+    <t>2026-07-16T08:21:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T08:21:58+00:00</t>
+    <t>2026-07-16T08:46:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T08:46:36+00:00</t>
+    <t>2026-07-16T10:52:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T10:52:32+00:00</t>
+    <t>2026-07-16T11:12:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T11:12:17+00:00</t>
+    <t>2026-07-16T21:31:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T21:31:30+00:00</t>
+    <t>2026-07-17T08:00:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T08:00:04+00:00</t>
+    <t>2026-07-17T11:25:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T11:25:46+00:00</t>
+    <t>2026-07-17T14:49:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T14:49:58+00:00</t>
+    <t>2026-07-19T17:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-19T17:20:25+00:00</t>
+    <t>2026-07-21T08:40:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:40:48+00:00</t>
+    <t>2026-07-21T15:50:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T15:50:20+00:00</t>
+    <t>2026-07-21T16:28:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:28:50+00:00</t>
+    <t>2026-07-21T16:53:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="84">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:53:48+00:00</t>
+    <t>2026-07-22T08:07:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -247,7 +247,10 @@
 </t>
   </si>
   <si>
-    <t>Transaction ExportArchivePortabilite</t>
+    <t>Documentation d'export permettant au fournisseur destinataire d'intégrer les données LGC du fournisseur sortant.</t>
+  </si>
+  <si>
+    <t>Transaction ExportArchivePortabilite.</t>
   </si>
   <si>
     <t>Base</t>
@@ -263,7 +266,7 @@
 </t>
   </si>
   <si>
-    <t>Documents permettant au fournisseur destinataire d'interpréter et d'intégrer les données (dictionnaire de données, mapping, dictionnaire de terminologies propriétaures, jeu d'échantillons)</t>
+    <t>Documents permettant au fournisseur destinataire d'interpréter et d'intégrer les données (dictionnaire de données, mapping, dictionnaire de terminologies propriétaures, jeu d'échantillons).</t>
   </si>
 </sst>
 </file>
@@ -746,13 +749,13 @@
         <v>76</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
@@ -802,7 +805,7 @@
         <v>73</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>74</v>
@@ -819,10 +822,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -830,7 +833,7 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G3" t="s" s="2">
         <v>75</v>
@@ -845,13 +848,13 @@
         <v>73</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -902,10 +905,10 @@
         <v>73</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH3" t="s" s="2">
         <v>75</v>

--- a/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T08:07:11+00:00</t>
+    <t>2026-07-22T10:39:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T10:39:39+00:00</t>
+    <t>2026-07-22T17:16:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -256,7 +256,7 @@
     <t>Base</t>
   </si>
   <si>
-    <t>pdlgc-documentation.documents</t>
+    <t>pdlgc-documentation.documentation</t>
   </si>
   <si>
     <t>1</t>
@@ -571,8 +571,8 @@
   <dimension ref="A1:AJ3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="26.91015625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="26.91015625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="30.0625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="30.0625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -602,7 +602,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="26.91015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="30.0625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>

--- a/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-documentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T17:16:50+00:00</t>
+    <t>2026-07-23T08:53:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
